--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
@@ -362,42 +362,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>E_PRENETA_a</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>E_BASNETA_a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>E_MEDIANETA_a</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>E_SUPNETA_a</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>E_PREBRUT_a</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>E_PRENETA_a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>E_BASBRUT_a</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>E_BASNETA_a</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>E_MEDIABRUT_a</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>E_MEDIANETA_a</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>E_SUPBRUT_a</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>E_SUPNETA_a</t>
         </is>
       </c>
     </row>
@@ -408,28 +408,28 @@
         </is>
       </c>
       <c r="B2">
+        <v>60.73665</v>
+      </c>
+      <c r="C2">
+        <v>95.67995000000001</v>
+      </c>
+      <c r="D2">
+        <v>85.68131</v>
+      </c>
+      <c r="E2">
+        <v>46.75521</v>
+      </c>
+      <c r="F2">
         <v>60.97237</v>
       </c>
-      <c r="C2">
-        <v>60.73665</v>
-      </c>
-      <c r="D2">
+      <c r="G2">
         <v>100.3462</v>
       </c>
-      <c r="E2">
-        <v>95.67995000000001</v>
-      </c>
-      <c r="F2">
+      <c r="H2">
         <v>103.3327</v>
       </c>
-      <c r="G2">
-        <v>85.68131</v>
-      </c>
-      <c r="H2">
+      <c r="I2">
         <v>66.18273000000001</v>
-      </c>
-      <c r="I2">
-        <v>46.75521</v>
       </c>
     </row>
     <row r="3">
@@ -439,28 +439,28 @@
         </is>
       </c>
       <c r="B3">
+        <v>60.66465</v>
+      </c>
+      <c r="C3">
+        <v>96.37263</v>
+      </c>
+      <c r="D3">
+        <v>82.9653</v>
+      </c>
+      <c r="E3">
+        <v>36.99422</v>
+      </c>
+      <c r="F3">
         <v>60.84592</v>
       </c>
-      <c r="C3">
-        <v>60.66465</v>
-      </c>
-      <c r="D3">
+      <c r="G3">
         <v>102.7205</v>
       </c>
-      <c r="E3">
-        <v>96.37263</v>
-      </c>
-      <c r="F3">
+      <c r="H3">
         <v>102.3659</v>
       </c>
-      <c r="G3">
-        <v>82.9653</v>
-      </c>
-      <c r="H3">
+      <c r="I3">
         <v>51.32948</v>
-      </c>
-      <c r="I3">
-        <v>36.99422</v>
       </c>
     </row>
     <row r="4">
@@ -470,28 +470,28 @@
         </is>
       </c>
       <c r="B4">
+        <v>63.31337</v>
+      </c>
+      <c r="C4">
+        <v>96.67014</v>
+      </c>
+      <c r="D4">
+        <v>83.54303</v>
+      </c>
+      <c r="E4">
+        <v>40.79392</v>
+      </c>
+      <c r="F4">
         <v>63.63274</v>
       </c>
-      <c r="C4">
-        <v>63.31337</v>
-      </c>
-      <c r="D4">
+      <c r="G4">
         <v>102.1852</v>
       </c>
-      <c r="E4">
-        <v>96.67014</v>
-      </c>
-      <c r="F4">
+      <c r="H4">
         <v>103.0196</v>
       </c>
-      <c r="G4">
-        <v>83.54303</v>
-      </c>
-      <c r="H4">
+      <c r="I4">
         <v>59.99437</v>
-      </c>
-      <c r="I4">
-        <v>40.79392</v>
       </c>
     </row>
     <row r="5">
@@ -504,25 +504,25 @@
         <v>54.73801</v>
       </c>
       <c r="C5">
+        <v>97.47588</v>
+      </c>
+      <c r="D5">
+        <v>87.18626</v>
+      </c>
+      <c r="E5">
+        <v>31.65969</v>
+      </c>
+      <c r="F5">
         <v>54.73801</v>
       </c>
-      <c r="D5">
+      <c r="G5">
         <v>103.0438</v>
       </c>
-      <c r="E5">
-        <v>97.47588</v>
-      </c>
-      <c r="F5">
+      <c r="H5">
         <v>102.5099</v>
       </c>
-      <c r="G5">
-        <v>87.18626</v>
-      </c>
-      <c r="H5">
+      <c r="I5">
         <v>41.70153</v>
-      </c>
-      <c r="I5">
-        <v>31.65969</v>
       </c>
     </row>
     <row r="6">
@@ -532,28 +532,28 @@
         </is>
       </c>
       <c r="B6">
+        <v>57.81759</v>
+      </c>
+      <c r="C6">
+        <v>94.21053000000001</v>
+      </c>
+      <c r="D6">
+        <v>83.13952999999999</v>
+      </c>
+      <c r="E6">
+        <v>35.41267</v>
+      </c>
+      <c r="F6">
         <v>58.30619</v>
       </c>
-      <c r="C6">
-        <v>57.81759</v>
-      </c>
-      <c r="D6">
+      <c r="G6">
         <v>100.8421</v>
       </c>
-      <c r="E6">
-        <v>94.21053000000001</v>
-      </c>
-      <c r="F6">
+      <c r="H6">
         <v>105.814</v>
       </c>
-      <c r="G6">
-        <v>83.13952999999999</v>
-      </c>
-      <c r="H6">
+      <c r="I6">
         <v>45.2975</v>
-      </c>
-      <c r="I6">
-        <v>35.41267</v>
       </c>
     </row>
     <row r="7">
@@ -563,28 +563,28 @@
         </is>
       </c>
       <c r="B7">
+        <v>54.55746</v>
+      </c>
+      <c r="C7">
+        <v>96.22332</v>
+      </c>
+      <c r="D7">
+        <v>83.88625</v>
+      </c>
+      <c r="E7">
+        <v>33.41543</v>
+      </c>
+      <c r="F7">
         <v>54.68956</v>
       </c>
-      <c r="C7">
-        <v>54.55746</v>
-      </c>
-      <c r="D7">
+      <c r="G7">
         <v>102.4631</v>
       </c>
-      <c r="E7">
-        <v>96.22332</v>
-      </c>
-      <c r="F7">
+      <c r="H7">
         <v>100.4739</v>
       </c>
-      <c r="G7">
-        <v>83.88625</v>
-      </c>
-      <c r="H7">
+      <c r="I7">
         <v>44.49918</v>
-      </c>
-      <c r="I7">
-        <v>33.41543</v>
       </c>
     </row>
     <row r="8">
@@ -594,28 +594,28 @@
         </is>
       </c>
       <c r="B8">
+        <v>57.7269</v>
+      </c>
+      <c r="C8">
+        <v>96.98155</v>
+      </c>
+      <c r="D8">
+        <v>86.22503</v>
+      </c>
+      <c r="E8">
+        <v>37.99664</v>
+      </c>
+      <c r="F8">
         <v>57.80867</v>
       </c>
-      <c r="C8">
-        <v>57.7269</v>
-      </c>
-      <c r="D8">
+      <c r="G8">
         <v>102.6831</v>
       </c>
-      <c r="E8">
-        <v>96.98155</v>
-      </c>
-      <c r="F8">
+      <c r="H8">
         <v>97.05573</v>
       </c>
-      <c r="G8">
-        <v>86.22503</v>
-      </c>
-      <c r="H8">
+      <c r="I8">
         <v>51.87465</v>
-      </c>
-      <c r="I8">
-        <v>37.99664</v>
       </c>
     </row>
     <row r="9">
@@ -625,28 +625,28 @@
         </is>
       </c>
       <c r="B9">
+        <v>51.80832</v>
+      </c>
+      <c r="C9">
+        <v>96.35294</v>
+      </c>
+      <c r="D9">
+        <v>84.81953</v>
+      </c>
+      <c r="E9">
+        <v>32.90141</v>
+      </c>
+      <c r="F9">
         <v>51.89874</v>
       </c>
-      <c r="C9">
-        <v>51.80832</v>
-      </c>
-      <c r="D9">
+      <c r="G9">
         <v>102.7647</v>
       </c>
-      <c r="E9">
-        <v>96.35294</v>
-      </c>
-      <c r="F9">
+      <c r="H9">
         <v>105.6263</v>
       </c>
-      <c r="G9">
-        <v>84.81953</v>
-      </c>
-      <c r="H9">
+      <c r="I9">
         <v>43.60563</v>
-      </c>
-      <c r="I9">
-        <v>32.90141</v>
       </c>
     </row>
     <row r="10">
@@ -656,28 +656,28 @@
         </is>
       </c>
       <c r="B10">
+        <v>65.29968</v>
+      </c>
+      <c r="C10">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="D10">
+        <v>89.28570999999999</v>
+      </c>
+      <c r="E10">
+        <v>40.83585</v>
+      </c>
+      <c r="F10">
         <v>65.45741</v>
       </c>
-      <c r="C10">
-        <v>65.29968</v>
-      </c>
-      <c r="D10">
+      <c r="G10">
         <v>102.3</v>
       </c>
-      <c r="E10">
-        <v>98.09999999999999</v>
-      </c>
-      <c r="F10">
+      <c r="H10">
         <v>102.7473</v>
       </c>
-      <c r="G10">
-        <v>89.28570999999999</v>
-      </c>
-      <c r="H10">
+      <c r="I10">
         <v>54.38066</v>
-      </c>
-      <c r="I10">
-        <v>40.83585</v>
       </c>
     </row>
     <row r="11">
@@ -690,25 +690,25 @@
         <v>64.24937</v>
       </c>
       <c r="C11">
+        <v>96.61563</v>
+      </c>
+      <c r="D11">
+        <v>87.41722</v>
+      </c>
+      <c r="E11">
+        <v>43.12914</v>
+      </c>
+      <c r="F11">
         <v>64.24937</v>
       </c>
-      <c r="D11">
+      <c r="G11">
         <v>101.3699</v>
       </c>
-      <c r="E11">
-        <v>96.61563</v>
-      </c>
-      <c r="F11">
+      <c r="H11">
         <v>99.00662</v>
       </c>
-      <c r="G11">
-        <v>87.41722</v>
-      </c>
-      <c r="H11">
+      <c r="I11">
         <v>57.78146</v>
-      </c>
-      <c r="I11">
-        <v>43.12914</v>
       </c>
     </row>
     <row r="12">
@@ -718,28 +718,28 @@
         </is>
       </c>
       <c r="B12">
+        <v>62.40876</v>
+      </c>
+      <c r="C12">
+        <v>95.36842</v>
+      </c>
+      <c r="D12">
+        <v>82.89474</v>
+      </c>
+      <c r="E12">
+        <v>32.08661</v>
+      </c>
+      <c r="F12">
         <v>62.77372</v>
       </c>
-      <c r="C12">
-        <v>62.40876</v>
-      </c>
-      <c r="D12">
+      <c r="G12">
         <v>100</v>
       </c>
-      <c r="E12">
-        <v>95.36842</v>
-      </c>
-      <c r="F12">
+      <c r="H12">
         <v>103.0702</v>
       </c>
-      <c r="G12">
-        <v>82.89474</v>
-      </c>
-      <c r="H12">
+      <c r="I12">
         <v>42.12598</v>
-      </c>
-      <c r="I12">
-        <v>32.08661</v>
       </c>
     </row>
     <row r="13">
@@ -749,28 +749,28 @@
         </is>
       </c>
       <c r="B13">
+        <v>58.88325</v>
+      </c>
+      <c r="C13">
+        <v>97.22851</v>
+      </c>
+      <c r="D13">
+        <v>89.53879999999999</v>
+      </c>
+      <c r="E13">
+        <v>43.69197</v>
+      </c>
+      <c r="F13">
         <v>58.96785</v>
       </c>
-      <c r="C13">
-        <v>58.88325</v>
-      </c>
-      <c r="D13">
+      <c r="G13">
         <v>100.6222</v>
       </c>
-      <c r="E13">
-        <v>97.22851</v>
-      </c>
-      <c r="F13">
+      <c r="H13">
         <v>105.3993</v>
       </c>
-      <c r="G13">
-        <v>89.53879999999999</v>
-      </c>
-      <c r="H13">
+      <c r="I13">
         <v>57.56417</v>
-      </c>
-      <c r="I13">
-        <v>43.69197</v>
       </c>
     </row>
     <row r="14">
@@ -780,28 +780,28 @@
         </is>
       </c>
       <c r="B14">
+        <v>60.81505</v>
+      </c>
+      <c r="C14">
+        <v>96.26719</v>
+      </c>
+      <c r="D14">
+        <v>85.85858</v>
+      </c>
+      <c r="E14">
+        <v>35.95506</v>
+      </c>
+      <c r="F14">
         <v>61.12852</v>
       </c>
-      <c r="C14">
-        <v>60.81505</v>
-      </c>
-      <c r="D14">
+      <c r="G14">
         <v>101.3752</v>
       </c>
-      <c r="E14">
-        <v>96.26719</v>
-      </c>
-      <c r="F14">
+      <c r="H14">
         <v>103.7037</v>
       </c>
-      <c r="G14">
-        <v>85.85858</v>
-      </c>
-      <c r="H14">
+      <c r="I14">
         <v>47.19101</v>
-      </c>
-      <c r="I14">
-        <v>35.95506</v>
       </c>
     </row>
     <row r="15">
@@ -814,25 +814,25 @@
         <v>58.98204</v>
       </c>
       <c r="C15">
+        <v>96.34146</v>
+      </c>
+      <c r="D15">
+        <v>87.35178000000001</v>
+      </c>
+      <c r="E15">
+        <v>37.26937</v>
+      </c>
+      <c r="F15">
         <v>58.98204</v>
       </c>
-      <c r="D15">
+      <c r="G15">
         <v>101.8293</v>
       </c>
-      <c r="E15">
-        <v>96.34146</v>
-      </c>
-      <c r="F15">
+      <c r="H15">
         <v>103.5573</v>
       </c>
-      <c r="G15">
-        <v>87.35178000000001</v>
-      </c>
-      <c r="H15">
+      <c r="I15">
         <v>44.09594</v>
-      </c>
-      <c r="I15">
-        <v>37.26937</v>
       </c>
     </row>
     <row r="16">
@@ -845,25 +845,25 @@
         <v>58.14536</v>
       </c>
       <c r="C16">
+        <v>98.11644</v>
+      </c>
+      <c r="D16">
+        <v>87.87878000000001</v>
+      </c>
+      <c r="E16">
+        <v>37.86078</v>
+      </c>
+      <c r="F16">
         <v>58.14536</v>
       </c>
-      <c r="D16">
+      <c r="G16">
         <v>103.5959</v>
       </c>
-      <c r="E16">
-        <v>98.11644</v>
-      </c>
-      <c r="F16">
+      <c r="H16">
         <v>101.0101</v>
       </c>
-      <c r="G16">
-        <v>87.87878000000001</v>
-      </c>
-      <c r="H16">
+      <c r="I16">
         <v>51.10357</v>
-      </c>
-      <c r="I16">
-        <v>37.86078</v>
       </c>
     </row>
     <row r="17">
@@ -873,28 +873,28 @@
         </is>
       </c>
       <c r="B17">
+        <v>64.70589</v>
+      </c>
+      <c r="C17">
+        <v>95.85687</v>
+      </c>
+      <c r="D17">
+        <v>89.84614999999999</v>
+      </c>
+      <c r="E17">
+        <v>40.69069</v>
+      </c>
+      <c r="F17">
         <v>64.70587999999999</v>
       </c>
-      <c r="C17">
-        <v>64.70589</v>
-      </c>
-      <c r="D17">
+      <c r="G17">
         <v>99.62335</v>
       </c>
-      <c r="E17">
-        <v>95.85687</v>
-      </c>
-      <c r="F17">
+      <c r="H17">
         <v>104.6154</v>
       </c>
-      <c r="G17">
-        <v>89.84614999999999</v>
-      </c>
-      <c r="H17">
+      <c r="I17">
         <v>53.45345</v>
-      </c>
-      <c r="I17">
-        <v>40.69069</v>
       </c>
     </row>
     <row r="18">
@@ -904,28 +904,28 @@
         </is>
       </c>
       <c r="B18">
+        <v>56.13295</v>
+      </c>
+      <c r="C18">
+        <v>97.20907</v>
+      </c>
+      <c r="D18">
+        <v>85.0386</v>
+      </c>
+      <c r="E18">
+        <v>40.54659</v>
+      </c>
+      <c r="F18">
         <v>56.37035</v>
       </c>
-      <c r="C18">
-        <v>56.13295</v>
-      </c>
-      <c r="D18">
+      <c r="G18">
         <v>103.0447</v>
       </c>
-      <c r="E18">
-        <v>97.20907</v>
-      </c>
-      <c r="F18">
+      <c r="H18">
         <v>104.6332</v>
       </c>
-      <c r="G18">
-        <v>85.0386</v>
-      </c>
-      <c r="H18">
+      <c r="I18">
         <v>54.37111</v>
-      </c>
-      <c r="I18">
-        <v>40.54659</v>
       </c>
     </row>
     <row r="19">
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="B19">
+        <v>58.34124</v>
+      </c>
+      <c r="C19">
+        <v>97.21178</v>
+      </c>
+      <c r="D19">
+        <v>81.99879</v>
+      </c>
+      <c r="E19">
+        <v>31.79487</v>
+      </c>
+      <c r="F19">
         <v>58.53081</v>
       </c>
-      <c r="C19">
-        <v>58.34124</v>
-      </c>
-      <c r="D19">
+      <c r="G19">
         <v>101.7231</v>
       </c>
-      <c r="E19">
-        <v>97.21178</v>
-      </c>
-      <c r="F19">
+      <c r="H19">
         <v>96.74894999999999</v>
       </c>
-      <c r="G19">
-        <v>81.99879</v>
-      </c>
-      <c r="H19">
+      <c r="I19">
         <v>40.80128</v>
-      </c>
-      <c r="I19">
-        <v>31.79487</v>
       </c>
     </row>
     <row r="20">
@@ -966,28 +966,28 @@
         </is>
       </c>
       <c r="B20">
+        <v>54.75234</v>
+      </c>
+      <c r="C20">
+        <v>97.35683</v>
+      </c>
+      <c r="D20">
+        <v>81.20301000000001</v>
+      </c>
+      <c r="E20">
+        <v>33.75594</v>
+      </c>
+      <c r="F20">
         <v>55.02008</v>
       </c>
-      <c r="C20">
-        <v>54.75234</v>
-      </c>
-      <c r="D20">
+      <c r="G20">
         <v>105.9912</v>
       </c>
-      <c r="E20">
-        <v>97.35683</v>
-      </c>
-      <c r="F20">
+      <c r="H20">
         <v>99.24812</v>
       </c>
-      <c r="G20">
-        <v>81.20301000000001</v>
-      </c>
-      <c r="H20">
+      <c r="I20">
         <v>45.00792</v>
-      </c>
-      <c r="I20">
-        <v>33.75594</v>
       </c>
     </row>
     <row r="21">
@@ -1000,25 +1000,25 @@
         <v>53.80117</v>
       </c>
       <c r="C21">
+        <v>97.55101999999999</v>
+      </c>
+      <c r="D21">
+        <v>83.60001</v>
+      </c>
+      <c r="E21">
+        <v>37.37166</v>
+      </c>
+      <c r="F21">
         <v>53.80117</v>
       </c>
-      <c r="D21">
+      <c r="G21">
         <v>103.2653</v>
       </c>
-      <c r="E21">
-        <v>97.55101999999999</v>
-      </c>
-      <c r="F21">
+      <c r="H21">
         <v>99.2</v>
       </c>
-      <c r="G21">
-        <v>83.60001</v>
-      </c>
-      <c r="H21">
+      <c r="I21">
         <v>49.89733</v>
-      </c>
-      <c r="I21">
-        <v>37.37166</v>
       </c>
     </row>
     <row r="22">
@@ -1028,28 +1028,28 @@
         </is>
       </c>
       <c r="B22">
+        <v>59.2638</v>
+      </c>
+      <c r="C22">
+        <v>97.59377000000001</v>
+      </c>
+      <c r="D22">
+        <v>82.24688</v>
+      </c>
+      <c r="E22">
+        <v>35.92302</v>
+      </c>
+      <c r="F22">
         <v>59.5092</v>
       </c>
-      <c r="C22">
-        <v>59.2638</v>
-      </c>
-      <c r="D22">
+      <c r="G22">
         <v>102.477</v>
       </c>
-      <c r="E22">
-        <v>97.59377000000001</v>
-      </c>
-      <c r="F22">
+      <c r="H22">
         <v>98.75172999999999</v>
       </c>
-      <c r="G22">
-        <v>82.24688</v>
-      </c>
-      <c r="H22">
+      <c r="I22">
         <v>47.32716</v>
-      </c>
-      <c r="I22">
-        <v>35.92302</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 19:44</t>
+    <t xml:space="preserve">2026-08-02 19:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-02 19:41</t>
+    <t xml:space="preserve">2026-08-05 10:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:34</t>
+    <t xml:space="preserve">2026-08-16 09:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:46</t>
+    <t xml:space="preserve">2026-08-19 11:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:41</t>
+    <t xml:space="preserve">2026-08-28 11:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
+++ b/output/graficos_educacion_tasas/comunal_e_matricula_a_2018_nuble.xlsx
@@ -117,7 +117,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:24</t>
+    <t xml:space="preserve">2026-09-06 17:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
